--- a/03_Tools/Watchlist_Ersatzbank_Monitor_v1.1.xlsx
+++ b/03_Tools/Watchlist_Ersatzbank_Monitor_v1.1.xlsx
@@ -928,7 +928,7 @@
     <row r="1" ht="21.95" customHeight="1" s="67">
       <c r="A1" s="80" t="inlineStr">
         <is>
-          <t>🦅  DYNASTIEDEPOT – WATCHLIST / ERSATZBANK MONITOR v1.1  |  Stand: 15.04.2026</t>
+          <t>🦅  DYNASTIEDEPOT – WATCHLIST / ERSATZBANK MONITOR v1.1  |  Stand: 27.04.2026</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="L13" s="39" t="inlineStr">
         <is>
-          <t>79 / DEFCON 3</t>
+          <t>76 / DEFCON 3</t>
         </is>
       </c>
       <c r="M13" s="40" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="N13" s="41" t="inlineStr">
         <is>
-          <t>P/FCF ~32x 🟢. Wide Moat [KB] 18/20. Score 79 — 1 Pkt unter 80-Schwelle. Re-Analyse Q1 Earnings 28.04.2026.</t>
+          <t>P/FCF ~32x 🟢. Wide Moat [KB] 18/20. Score 76 (post-DEFCON v3.5 Audit 16.04.2026: 79→76, Goodwill-Malus Ansys-Akquisition -3 Pkt). Re-Analyse Q1 Earnings 28.04.2026.</t>
         </is>
       </c>
       <c r="O13" s="42" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="L15" s="39" t="inlineStr">
         <is>
-          <t>79 / DEFCON 3</t>
+          <t>74 / DEFCON 3</t>
         </is>
       </c>
       <c r="M15" s="40" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="N15" s="41" t="inlineStr">
         <is>
-          <t>P/FCF ~22x 🟢. Wide Moat 19/20. Ratings-Duopol. Earnings 28.04.2026 → Katalysator. Re-Analyse bei Score ≥80.</t>
+          <t>P/FCF ~22x 🟢. Wide Moat 19/20. Ratings-Duopol. Score 74 (post-DEFCON v3.5 Audit 16.04.2026: 77→74, ROIC-Verzerrung durch IHS Markit M&amp;A-Goodwill, Non-GAAP ~82). Earnings 28.04.2026 → Katalysator. Re-Analyse bei Score ≥80.</t>
         </is>
       </c>
       <c r="O15" s="42" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>70 / DEFCON 3</t>
+          <t>67 / DEFCON 3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Vollanalyse 03.04.2026. Score 70 / DEFCON 3. Fwd P/FCF ~19x 🟢 (nach -52% Crash). ROIC 75% exzellent. 10b5-1 Cashless-Exercise erkannt. Re-Analyse bei VEEV-Schwäche.</t>
+          <t>Vollanalyse 03.04.2026. Score 67 (post-DEFCON v3.5 Audit 16.04.2026: 70→67, TTM-Verzerrung Kurscrash -52%). Fwd P/FCF ~19x 🟢. ROIC 75% exzellent. Quick-Screener-Sweep 27.04.2026: ROIC 42-45% TTM bestätigt, weiterer Kursfall -48% YTD trotz +40% EPS-Growth = Multiple-Compression.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="23" ht="15.95" customHeight="1" s="67">
       <c r="A23" s="62" t="inlineStr">
         <is>
-          <t>⚡  QuickScreen Ergebnis – 15.04.2026  |  Filter: P/FCF ≤35🟢/≤45🟡/&gt;45🔴  |  ROIC ≥15%🟢/≥12%🟡/&lt;12%🔴  |  Moat Wide🟢/Narrow🟡/None🔴</t>
+          <t>⚡  QuickScreen Ergebnis – 27.04.2026  |  Filter: P/FCF ≤35🟢/≤45🟡/&gt;45🔴  |  ROIC ≥15%🟢/≥12%🟡/&lt;12%🔴  |  Moat Wide🟢/Narrow🟡/None🔴</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H28" s="51" t="inlineStr">
         <is>
-          <t>Score 79. 1 Pkt unter 80-Schwelle. Re-Analyse Mai 2026.</t>
+          <t>Score 76 (post-v3.5 Audit). 4 Pkt unter 80-Schwelle. Re-Analyse Q1 Earnings 28.04.2026.</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="H29" s="51" t="inlineStr">
         <is>
-          <t>Score 79. Earnings 28.04.2026 → Katalysator-Check.</t>
+          <t>Score 74 (post-v3.5 Audit). Earnings 28.04.2026 → Katalysator-Check.</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Score 70 / DEFCON 3. Fwd P/FCF ~19x 🟢. ROIC 75% exzellent. Re-Analyse bei VEEV-Schwäche.</t>
+          <t>Score 67 / DEFCON 3 (post-v3.5 Audit). Fwd P/FCF ~19x 🟢. ROIC 75% exzellent. Re-Analyse bei VEEV-Schwäche.</t>
         </is>
       </c>
     </row>

--- a/03_Tools/Watchlist_Ersatzbank_Monitor_v1.1.xlsx
+++ b/03_Tools/Watchlist_Ersatzbank_Monitor_v1.1.xlsx
@@ -928,7 +928,7 @@
     <row r="1" ht="21.95" customHeight="1" s="67">
       <c r="A1" s="80" t="inlineStr">
         <is>
-          <t>🦅  DYNASTIEDEPOT – WATCHLIST / ERSATZBANK MONITOR v1.1  |  Stand: 27.04.2026</t>
+          <t>🦅  DYNASTIEDEPOT – WATCHLIST / ERSATZBANK MONITOR v1.1  |  Stand: 14.05.2026 — Refresh v3.2</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
     <row r="3" ht="14.1" customHeight="1" s="67">
       <c r="A3" s="68" t="inlineStr">
         <is>
-          <t>Ersatzbank: 8 Ticker  |  Watchlist: 8 Ticker (inkl. FICO neu)  |  Keine Zuteilung: 2 Ticker  |  🟢 6 Einstieg  🟡 10 Beobachten  🔴 2 Kein Einstieg</t>
+          <t>Ersatzbank: 9 Ticker  |  Watchlist: 3 Ticker (SNPS Adjacent · PEGA · SPGI)  |  🟢 11 Einstieg  🔴 1 ROT (TYL Audit-Doku)</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Keine Zuteilung</t>
+          <t>Ersatzbank AVGO (exkl. MRVL-Strk. 14.05.)</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Ersatzbank VEEV</t>
+          <t>Ersatzbank TMO exkl. (Reassign 14.05.)</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>~30,2x [QS]</t>
+          <t>30,2x [QS 25.04.]</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>~43% [QS]</t>
+          <t>43% [QS 25.04.]</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>—⁶</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>Ersatzbank SU</t>
+          <t>Ersatzbank SU (deferred PIPELINE #63 post-21.05.)</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
@@ -1565,47 +1565,47 @@
     <row r="12" ht="21.95" customHeight="1" s="67">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B12" s="74" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Ersatzbank AVGO</t>
+          <t>Ersatzbank MSFT (NEU 14.05.)</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>~52x [KB]</t>
+          <t>~10 [QS 14.05.]</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>~2,7% [KB]</t>
+          <t>35,97% [QS 14.05.]</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>~50% [KB]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>~22% [KB]</t>
+          <t>~9% (Morningstar)</t>
         </is>
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>Narrow [KB]</t>
+          <t>Wide ✅ (digital media)</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
-          <t>Narrow [KB]</t>
+          <t>Wide [QS]</t>
         </is>
       </c>
       <c r="J12" s="27" t="inlineStr">
@@ -1642,47 +1642,47 @@
     <row r="13" ht="21.95" customHeight="1" s="67">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B13" s="79" t="inlineStr">
         <is>
-          <t>Synopsys Inc.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Watchlist ASML-Ers.</t>
+          <t>Ersatzbank ASML (NEU 14.05.)</t>
         </is>
       </c>
       <c r="D13" s="37" t="inlineStr">
         <is>
-          <t>~32x [KB]</t>
+          <t>~25-40 [QS 14.05.]</t>
         </is>
       </c>
       <c r="E13" s="37" t="inlineStr">
         <is>
-          <t>~18–22% [KB]</t>
+          <t>73,08% [QS 14.05.]</t>
         </is>
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>~82% [KB]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="37" t="inlineStr">
         <is>
-          <t>~15–18% [KB]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="37" t="inlineStr">
         <is>
-          <t>Wide [KB]</t>
+          <t>Wide ✅ (Wafer-Inspection-Monopol)</t>
         </is>
       </c>
       <c r="I13" s="37" t="inlineStr">
         <is>
-          <t>Wide [KB]</t>
+          <t>Wide [QS]</t>
         </is>
       </c>
       <c r="J13" s="38" t="inlineStr">
@@ -1719,47 +1719,47 @@
     <row r="14" ht="21.95" customHeight="1" s="67">
       <c r="A14" s="34" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B14" s="79" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>Watchlist Slot-16</t>
+          <t>Ersatzbank VEEV (NEU 14.05.)</t>
         </is>
       </c>
       <c r="D14" s="37" t="inlineStr">
         <is>
-          <t>~15x [KB]</t>
+          <t>44,64 [QS 14.05.]</t>
         </is>
       </c>
       <c r="E14" s="37" t="inlineStr">
         <is>
-          <t>~75% [KB]</t>
+          <t>35,27% [QS 14.05.]</t>
         </is>
       </c>
       <c r="F14" s="37" t="inlineStr">
         <is>
-          <t>~76% [KB]</t>
+          <t>63,4% Q1 2026</t>
         </is>
       </c>
       <c r="G14" s="37" t="inlineStr">
         <is>
-          <t>~5–8% [KB]</t>
+          <t>~8% (Guide)</t>
         </is>
       </c>
       <c r="H14" s="37" t="inlineStr">
         <is>
-          <t>Narrow [KB]</t>
+          <t>Wide ✅ (Vet-Diag-Monopol 45%)</t>
         </is>
       </c>
       <c r="I14" s="37" t="inlineStr">
         <is>
-          <t>Narrow [KB]</t>
+          <t>Wide [QS]</t>
         </is>
       </c>
       <c r="J14" s="38" t="inlineStr">
@@ -1796,37 +1796,37 @@
     <row r="15" ht="21.95" customHeight="1" s="67">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B15" s="79" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Synopsys Inc.</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Adjacent-Slot Semi-Software (Reassign 14.05.)</t>
         </is>
       </c>
       <c r="D15" s="37" t="inlineStr">
         <is>
-          <t>~22x [KB]</t>
+          <t>~32x [KB]</t>
         </is>
       </c>
       <c r="E15" s="37" t="inlineStr">
         <is>
+          <t>~18–22% [KB]</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>~82% [KB]</t>
+        </is>
+      </c>
+      <c r="G15" s="37" t="inlineStr">
+        <is>
           <t>~15–18% [KB]</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>~65–68% [KB]</t>
-        </is>
-      </c>
-      <c r="G15" s="37" t="inlineStr">
-        <is>
-          <t>~14–17% [KB]</t>
         </is>
       </c>
       <c r="H15" s="37" t="inlineStr">
@@ -1873,47 +1873,47 @@
     <row r="16" ht="21.95" customHeight="1" s="67">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B16" s="79" t="inlineStr">
         <is>
-          <t>Alphabet A</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>Watchlist FLAG</t>
+          <t>Watchlist Slot-16</t>
         </is>
       </c>
       <c r="D16" s="37" t="inlineStr">
         <is>
-          <t>~45x [KB]</t>
+          <t>~15x [KB]</t>
         </is>
       </c>
       <c r="E16" s="37" t="inlineStr">
         <is>
-          <t>~28% [KB]</t>
+          <t>~75% [KB]</t>
         </is>
       </c>
       <c r="F16" s="37" t="inlineStr">
         <is>
-          <t>~60% [KB]</t>
+          <t>~76% [KB]</t>
         </is>
       </c>
       <c r="G16" s="37" t="inlineStr">
         <is>
-          <t>~17% [KB]</t>
+          <t>~5–8% [KB]</t>
         </is>
       </c>
       <c r="H16" s="37" t="inlineStr">
         <is>
-          <t>Wide [KB]</t>
+          <t>Narrow [KB]</t>
         </is>
       </c>
       <c r="I16" s="37" t="inlineStr">
         <is>
-          <t>Wide [KB]</t>
+          <t>Narrow [KB]</t>
         </is>
       </c>
       <c r="J16" s="38" t="inlineStr">
@@ -1950,47 +1950,47 @@
     <row r="17" ht="21.95" customHeight="1" s="67">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B17" s="79" t="inlineStr">
         <is>
-          <t>Honeywell Intl.</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Watchlist (Re-Score #62 prio 1)</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
         <is>
-          <t>~26x [KB]</t>
+          <t>~22x [KB stale]</t>
         </is>
       </c>
       <c r="E17" s="37" t="inlineStr">
         <is>
-          <t>~12–15% [KB]</t>
+          <t>~15–18% [KB stale]</t>
         </is>
       </c>
       <c r="F17" s="37" t="inlineStr">
         <is>
-          <t>~37% [KB]</t>
+          <t>~65–68% [KB]</t>
         </is>
       </c>
       <c r="G17" s="37" t="inlineStr">
         <is>
-          <t>~2% [KB]</t>
+          <t>~14–17% [KB]</t>
         </is>
       </c>
       <c r="H17" s="40" t="inlineStr">
         <is>
-          <t>8 / Wide ✅</t>
+          <t>Wide [KB]</t>
         </is>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
-          <t>Wide ✅</t>
+          <t>Wide [KB]</t>
         </is>
       </c>
       <c r="J17" s="38" t="inlineStr">
@@ -2025,51 +2025,15 @@
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" s="67">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B18" s="79" t="inlineStr">
-        <is>
-          <t>SAP SE</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>Watchlist VEEV-Ers.</t>
-        </is>
-      </c>
-      <c r="D18" s="37" t="inlineStr">
-        <is>
-          <t>~35–42x [KB]</t>
-        </is>
-      </c>
-      <c r="E18" s="37" t="inlineStr">
-        <is>
-          <t>~10–14% [KB]</t>
-        </is>
-      </c>
-      <c r="F18" s="37" t="inlineStr">
-        <is>
-          <t>~71% [KB]</t>
-        </is>
-      </c>
-      <c r="G18" s="37" t="inlineStr">
-        <is>
-          <t>~8% [KB]</t>
-        </is>
-      </c>
-      <c r="H18" s="46" t="inlineStr">
-        <is>
-          <t>Wide [~]</t>
-        </is>
-      </c>
-      <c r="I18" s="46" t="inlineStr">
-        <is>
-          <t>Wide [~]</t>
-        </is>
-      </c>
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="79" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="46" t="n"/>
+      <c r="I18" s="46" t="n"/>
       <c r="J18" s="38" t="inlineStr">
         <is>
           <t>n.a.</t>
@@ -2102,51 +2066,15 @@
       </c>
     </row>
     <row r="19" ht="21.95" customHeight="1" s="67">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>EXPN</t>
-        </is>
-      </c>
-      <c r="B19" s="79" t="inlineStr">
-        <is>
-          <t>Experian</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>Watchlist</t>
-        </is>
-      </c>
-      <c r="D19" s="38" t="inlineStr">
-        <is>
-          <t>FETCH</t>
-        </is>
-      </c>
-      <c r="E19" s="38" t="inlineStr">
-        <is>
-          <t>FETCH</t>
-        </is>
-      </c>
-      <c r="F19" s="38" t="inlineStr">
-        <is>
-          <t>FETCH</t>
-        </is>
-      </c>
-      <c r="G19" s="38" t="inlineStr">
-        <is>
-          <t>FETCH</t>
-        </is>
-      </c>
-      <c r="H19" s="46" t="inlineStr">
-        <is>
-          <t>Wide [~]</t>
-        </is>
-      </c>
-      <c r="I19" s="46" t="inlineStr">
-        <is>
-          <t>Wide [~]</t>
-        </is>
-      </c>
+      <c r="A19" s="34" t="n"/>
+      <c r="B19" s="79" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="46" t="n"/>
       <c r="J19" s="47" t="inlineStr">
         <is>
           <t>→ Fetch</t>
@@ -2179,51 +2107,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>FICO</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Fair Isaac Corp.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Watchlist VEEV-Ers. #1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>~19x Fwd [V]</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>~75% [V]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>~82% [V]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>~9% [V]</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Wide [V]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>n.a.</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Nein</t>
@@ -2262,7 +2145,7 @@
     <row r="23" ht="15.95" customHeight="1" s="67">
       <c r="A23" s="62" t="inlineStr">
         <is>
-          <t>⚡  QuickScreen Ergebnis – 27.04.2026  |  Filter: P/FCF ≤35🟢/≤45🟡/&gt;45🔴  |  ROIC ≥15%🟢/≥12%🟡/&lt;12%🔴  |  Moat Wide🟢/Narrow🟡/None🔴</t>
+          <t>⚡  QuickScreen Ergebnis – 14.05.2026 (Refresh v3.2)  |  Filter: P/FCF ≤35🟢/≤45🟡/&gt;45🔴  |  ROIC ≥15%🟢/≥12%🟡/&lt;12%🔴  |  Moat Wide🟢/Narrow🟡/None🔴</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2271,7 @@
       </c>
       <c r="H26" s="51" t="inlineStr">
         <is>
-          <t>QuickScan 25.04.2026 — alle 3 Filter ✅. !Analysiere starten bei V-D2-Downshift oder Slot-Freigabe.</t>
+          <t>QuickScan 25.04.→Carryover 14.05. — alle 3 Filter ✅. !Analysiere bei V-D2-Persistenz oder Slot-Freigabe.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2288,7 @@
       </c>
       <c r="C27" s="49" t="inlineStr">
         <is>
-          <t>Ersatzbank SU</t>
+          <t>Ersatzbank SU (deferred #63)</t>
         </is>
       </c>
       <c r="D27" s="49" t="inlineStr">
@@ -2430,7 +2313,7 @@
       </c>
       <c r="H27" s="51" t="inlineStr">
         <is>
-          <t>Günstige Bewertung. Moat [~] → Live-Fetch empfohlen.</t>
+          <t>Deferred PIPELINE #63 post-Q2 ~21.05. + !QuickCheck Tag+1.</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2330,7 @@
       </c>
       <c r="C28" s="49" t="inlineStr">
         <is>
-          <t>Watchlist ASML</t>
+          <t>Adjacent-Slot Semi-Software</t>
         </is>
       </c>
       <c r="D28" s="49" t="inlineStr">
@@ -2472,7 +2355,7 @@
       </c>
       <c r="H28" s="51" t="inlineStr">
         <is>
-          <t>Score 76 (post-v3.5 Audit). 4 Pkt unter 80-Schwelle. Re-Analyse Q1 Earnings 28.04.2026.</t>
+          <t>Score 76 (16.04. stale, Re-Score PIPELINE #62 prio 2). Adjacent-Etikette ab 14.05.</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2372,7 @@
       </c>
       <c r="C29" s="49" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Watchlist (Re-Score #62 prio 1)</t>
         </is>
       </c>
       <c r="D29" s="49" t="inlineStr">
@@ -2514,7 +2397,7 @@
       </c>
       <c r="H29" s="51" t="inlineStr">
         <is>
-          <t>Score 74 (post-v3.5 Audit). Earnings 28.04.2026 → Katalysator-Check.</t>
+          <t>Score 74 (16.04. stale). Q1 28.04. Earnings overdue → #62 Re-Score post-14.-28.05.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2456,7 @@
       </c>
       <c r="C31" s="53" t="inlineStr">
         <is>
-          <t>Ersatzbank VEEV</t>
+          <t>Ersatzbank TMO exkl. (Reassign 14.05.)</t>
         </is>
       </c>
       <c r="D31" s="53" t="inlineStr">
@@ -2598,7 +2481,7 @@
       </c>
       <c r="H31" s="55" t="inlineStr">
         <is>
-          <t>P/FCF Grenzfall. Bevorzugter VEEV-Ersatz. Re-Screen Q2.</t>
+          <t>P/FCF Grenzfall. Exklusiv TMO-Ersatz seit 14.05. (VEEV-Doppel entfernt, IDXX übernimmt VEEV).</t>
         </is>
       </c>
     </row>
@@ -2647,111 +2530,111 @@
     <row r="33" ht="45" customHeight="1" s="67">
       <c r="A33" s="52" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B33" s="53" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C33" s="53" t="inlineStr">
         <is>
-          <t>Watchlist Slot-16</t>
+          <t>Ersatzbank MSFT (NEU 14.05.)</t>
         </is>
       </c>
       <c r="D33" s="53" t="inlineStr">
         <is>
-          <t>🟢 ~15x</t>
+          <t>🟢 ~10</t>
         </is>
       </c>
       <c r="E33" s="53" t="inlineStr">
         <is>
-          <t>🟢 ~75%</t>
+          <t>🟢 35,97%</t>
         </is>
       </c>
       <c r="F33" s="53" t="inlineStr">
         <is>
-          <t>🟡 Narrow</t>
+          <t>🟢 Wide</t>
         </is>
       </c>
       <c r="G33" s="54" t="inlineStr">
         <is>
-          <t>🟡 Beobachten</t>
+          <t>🟢 Einstieg prüfen</t>
         </is>
       </c>
       <c r="H33" s="55" t="inlineStr">
         <is>
-          <t>Score 85! Moat-Debatte. Earnings Mai 2026 = Entscheidung.</t>
+          <t>QuickCheck 14.05. — alle 3 Filter ✅. Software-Plattform ohne Hyperscaler-CapEx. !Analysiere bei MSFT-FLAG-Resolve oder Slot-Freigabe.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1" s="67">
       <c r="A34" s="52" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B34" s="53" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C34" s="53" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Ersatzbank ASML (NEU 14.05.)</t>
         </is>
       </c>
       <c r="D34" s="53" t="inlineStr">
         <is>
-          <t>🟢 ~26x</t>
+          <t>🟡 ~25-40 Range (EV/FCF 44.5)</t>
         </is>
       </c>
       <c r="E34" s="53" t="inlineStr">
         <is>
-          <t>🟡 ~12–15%</t>
+          <t>🟢 73,08%</t>
         </is>
       </c>
       <c r="F34" s="53" t="inlineStr">
         <is>
-          <t>🟢 Wide 8/10</t>
+          <t>🟢 Wide</t>
         </is>
       </c>
       <c r="G34" s="54" t="inlineStr">
         <is>
-          <t>🟡 Beobachten</t>
+          <t>🟢 Einstieg prüfen</t>
         </is>
       </c>
       <c r="H34" s="56" t="inlineStr">
         <is>
-          <t>⭐ Wide Moat ✅ (neu – vormals Narrow!). Post-Spinoff abwarten.</t>
+          <t>QuickCheck 14.05. — Wafer-Inspection-Monopol. 1 Gelb akzeptabel. !Analysiere bei ASML-Slot-Freigabe.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1" s="67">
       <c r="A35" s="52" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B35" s="53" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C35" s="53" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Ersatzbank VEEV (NEU 14.05.)</t>
         </is>
       </c>
       <c r="D35" s="53" t="inlineStr">
         <is>
-          <t>🟡 ~35–42x</t>
+          <t>🟡 44,64</t>
         </is>
       </c>
       <c r="E35" s="53" t="inlineStr">
         <is>
-          <t>🔴 ~10–14%</t>
+          <t>🟢 35,27%</t>
         </is>
       </c>
       <c r="F35" s="53" t="inlineStr">
@@ -2761,44 +2644,44 @@
       </c>
       <c r="G35" s="54" t="inlineStr">
         <is>
-          <t>🟡 Beobachten</t>
+          <t>🟢 Einstieg prüfen</t>
         </is>
       </c>
       <c r="H35" s="55" t="inlineStr">
         <is>
-          <t>ROIC &lt; 12% 🔴. P/FCF Grenzfall. ZTS bevorzugt.</t>
+          <t>QuickCheck 14.05. — Vet-Diag-Monopol Catalyst-Platform. P/FCF 10J-Median 64,87 → historisch günstig. GF-Score 99/100. User-Vorschlag post-TYL-Rot.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1" s="67">
       <c r="A36" s="52" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="B36" s="53" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C36" s="53" t="inlineStr">
         <is>
-          <t>Keine Zuteilung</t>
+          <t>Watchlist Slot-16</t>
         </is>
       </c>
       <c r="D36" s="53" t="inlineStr">
         <is>
-          <t>🟡 ~42x</t>
+          <t>🟢 ~15x</t>
         </is>
       </c>
       <c r="E36" s="53" t="inlineStr">
         <is>
-          <t>🟢 ~75–90%</t>
+          <t>🟢 ~75%</t>
         </is>
       </c>
       <c r="F36" s="53" t="inlineStr">
         <is>
-          <t>🟢 Wide</t>
+          <t>🟡 Narrow</t>
         </is>
       </c>
       <c r="G36" s="54" t="inlineStr">
@@ -2808,39 +2691,39 @@
       </c>
       <c r="H36" s="55" t="inlineStr">
         <is>
-          <t>Keine Zuteilung – Konzentrationsrisiko. Beobachten.</t>
+          <t>Score 85! Moat-Debatte. Earnings Mai 2026 = Entscheidung.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1" s="67">
       <c r="A37" s="52" t="inlineStr">
         <is>
-          <t>EXPN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B37" s="53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C37" s="53" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Ersatzbank AVGO (exkl. MRVL)</t>
         </is>
       </c>
       <c r="D37" s="53" t="inlineStr">
         <is>
-          <t>→ Fetch</t>
+          <t>🟡 ~42x</t>
         </is>
       </c>
       <c r="E37" s="53" t="inlineStr">
         <is>
-          <t>→ Fetch</t>
+          <t>🟢 ~75–90%</t>
         </is>
       </c>
       <c r="F37" s="53" t="inlineStr">
         <is>
-          <t>🟢 Wide [~]</t>
+          <t>🟢 Wide</t>
         </is>
       </c>
       <c r="G37" s="54" t="inlineStr">
@@ -2850,34 +2733,34 @@
       </c>
       <c r="H37" s="55" t="inlineStr">
         <is>
-          <t>Alle Metriken ausstehend. EU-Ticker. Live-Fetch nötig.</t>
+          <t>Konzentrationsrisiko mit AVGO. MRVL aus §5-Doppel-Designation entfernt 14.05.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1" s="67">
       <c r="A38" s="57" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B38" s="58" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C38" s="58" t="inlineStr">
         <is>
-          <t>Watchlist FLAG</t>
+          <t>REJECTED 14.05. (kein §6-Eintrag)</t>
         </is>
       </c>
       <c r="D38" s="58" t="inlineStr">
         <is>
-          <t>🟡 ~45x</t>
+          <t>n.v.</t>
         </is>
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>🟢 ~28%</t>
+          <t>🔴 4,84-6,1% (GuruFocus konvergent)</t>
         </is>
       </c>
       <c r="F38" s="58" t="inlineStr">
@@ -2887,56 +2770,24 @@
       </c>
       <c r="G38" s="59" t="inlineStr">
         <is>
-          <t>🔴 FLAG / Kein Einstieg</t>
+          <t>🔴 Rot — kein Einstieg</t>
         </is>
       </c>
       <c r="H38" s="60" t="inlineStr">
         <is>
-          <t>🛑 FLAG CapEx 74–79% OCF. Kein Einstieg trotz gutem Moat.</t>
+          <t>ROIC &lt; WACC (8,99%) = value-destroying. §12 (b) Add verboten. StockAnalysis 8,86% hard-excluded per sources.md §7. Audit-Doku-Eintrag.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1" s="67">
-      <c r="A39" s="57" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="B39" s="58" t="inlineStr">
-        <is>
-          <t>Marvell Tech.</t>
-        </is>
-      </c>
-      <c r="C39" s="58" t="inlineStr">
-        <is>
-          <t>Ersatzbank AVGO</t>
-        </is>
-      </c>
-      <c r="D39" s="58" t="inlineStr">
-        <is>
-          <t>🔴 ~52x</t>
-        </is>
-      </c>
-      <c r="E39" s="58" t="inlineStr">
-        <is>
-          <t>🔴 ~2,7%</t>
-        </is>
-      </c>
-      <c r="F39" s="58" t="inlineStr">
-        <is>
-          <t>🟡 Narrow</t>
-        </is>
-      </c>
-      <c r="G39" s="59" t="inlineStr">
-        <is>
-          <t>🔴 Kein Einstieg</t>
-        </is>
-      </c>
-      <c r="H39" s="61" t="inlineStr">
-        <is>
-          <t>3/3 Filter rot/gelb. ROIC + P/FCF + Narrow Moat = aussortiert.</t>
-        </is>
-      </c>
+      <c r="A39" s="57" t="n"/>
+      <c r="B39" s="58" t="n"/>
+      <c r="C39" s="58" t="n"/>
+      <c r="D39" s="58" t="n"/>
+      <c r="E39" s="58" t="n"/>
+      <c r="F39" s="58" t="n"/>
+      <c r="G39" s="59" t="n"/>
+      <c r="H39" s="61" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
